--- a/부품_대량등록_양식.xlsx
+++ b/부품_대량등록_양식.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\마누스 자재관리 어플개발\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\클로드 코워크\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA5421D-D1A8-443F-BBA2-90D2338559E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D29C3C-C71F-4743-AF71-BCFDDCC60CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="295">
   <si>
     <t>부품 대량 등록/업데이트 양식</t>
   </si>
@@ -69,240 +69,18 @@
     <t>비고</t>
   </si>
   <si>
-    <t>11077CO</t>
-  </si>
-  <si>
     <t>세종기업</t>
   </si>
   <si>
-    <t>락링커버_CR</t>
-  </si>
-  <si>
-    <t>ABS+Cr(PNC1),</t>
-  </si>
-  <si>
-    <t>11390NO</t>
-  </si>
-  <si>
-    <t>디앤이</t>
-  </si>
-  <si>
-    <t>샹크너트</t>
-  </si>
-  <si>
-    <t>ABS GF10%_M35x1.5</t>
-  </si>
-  <si>
-    <t>11393CO</t>
-  </si>
-  <si>
-    <t>태산테크</t>
-  </si>
-  <si>
-    <t>QAA핸들_CR</t>
-  </si>
-  <si>
-    <t>ABS+CR</t>
-  </si>
-  <si>
-    <t>11393NO-2</t>
-  </si>
-  <si>
-    <t>QAA핸들_도금용</t>
-  </si>
-  <si>
-    <t>ABS</t>
-  </si>
-  <si>
-    <t>11394CO</t>
-  </si>
-  <si>
-    <t>QAA핸들캡_CR</t>
-  </si>
-  <si>
-    <t>11394CO-P</t>
-  </si>
-  <si>
-    <t>우신산업</t>
-  </si>
-  <si>
-    <t>QAA핸들캡_CR_청적인쇄</t>
-  </si>
-  <si>
-    <t>11394NO-2</t>
-  </si>
-  <si>
-    <t>QAA핸들캡_도금용</t>
-  </si>
-  <si>
-    <t>21006CO-E</t>
-  </si>
-  <si>
-    <t>태희금속</t>
-  </si>
-  <si>
-    <t>7500토수구_긴것_0.382(QAC)</t>
-  </si>
-  <si>
-    <t>Cr(BNC1)</t>
-  </si>
-  <si>
-    <t>21006NO</t>
-  </si>
-  <si>
-    <t>성진밸브산업</t>
-  </si>
-  <si>
-    <t>CAC203 중량:0.382Kg  무두 5*8</t>
-  </si>
-  <si>
-    <t>21006NO-C</t>
-  </si>
-  <si>
-    <t>대림금속</t>
-  </si>
-  <si>
-    <t>21006NO-D</t>
-  </si>
-  <si>
-    <t>대용연마</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>21006NO-S</t>
-  </si>
-  <si>
-    <t>수성인더스트리</t>
-  </si>
-  <si>
-    <t>21195CO-E</t>
-  </si>
-  <si>
-    <t>QAC몸통</t>
-  </si>
-  <si>
-    <t>21195NO-1</t>
-  </si>
-  <si>
-    <t>QAC바디(주조+가공)</t>
-  </si>
-  <si>
-    <t>21195NO-D</t>
-  </si>
-  <si>
-    <t>22006CO-E</t>
-  </si>
-  <si>
-    <t>Ø35(7375샹크)_단조</t>
-  </si>
-  <si>
-    <t>22006NO</t>
-  </si>
-  <si>
-    <t>대동테크</t>
-  </si>
-  <si>
-    <t>C3771BEØ35*3200 중량:0.318kg</t>
-  </si>
-  <si>
-    <t>22021NO</t>
-  </si>
-  <si>
-    <t>Ø35락링(수출용)</t>
-  </si>
-  <si>
-    <t>C3771BEØ23 83g</t>
-  </si>
-  <si>
-    <t>23061NO</t>
-  </si>
-  <si>
-    <t>대진금속</t>
-  </si>
-  <si>
-    <t>신)토수구연결니쁠_15.6</t>
-  </si>
-  <si>
-    <t>AN-111(2개) + P-10</t>
-  </si>
-  <si>
-    <t>베스트엔퍼스트</t>
-  </si>
-  <si>
-    <t>41024NO</t>
-  </si>
-  <si>
     <t>선영고무</t>
   </si>
   <si>
-    <t>에어레이터평패킹21x15x2.4t</t>
-  </si>
-  <si>
-    <t>NBR외Ø21x내Ø15x두2.4</t>
-  </si>
-  <si>
-    <t>41074NO</t>
-  </si>
-  <si>
-    <t>바디부패킹-QAA</t>
-  </si>
-  <si>
-    <t>49*38*2T_NBR 80</t>
-  </si>
-  <si>
-    <t>41627NO</t>
-  </si>
-  <si>
-    <t>오링 AN-111</t>
-  </si>
-  <si>
-    <t>Ø10.8x2.62</t>
-  </si>
-  <si>
-    <t>41630NO</t>
-  </si>
-  <si>
-    <t>오링 P-10</t>
-  </si>
-  <si>
-    <t>Ø9.8x1.9</t>
-  </si>
-  <si>
-    <t>43022NO</t>
-  </si>
-  <si>
-    <t>샤워EVA用PAD WHITE(47*35*3T)-QAA</t>
-  </si>
-  <si>
-    <t>EVA47X35X3T</t>
-  </si>
-  <si>
-    <t>51007NO</t>
-  </si>
-  <si>
     <t>대호금속</t>
   </si>
   <si>
-    <t>무두볼트 5*8</t>
-  </si>
-  <si>
-    <t>SUS304M5x.8-8mm</t>
-  </si>
-  <si>
-    <t>51054NO</t>
-  </si>
-  <si>
-    <t>삼일공사</t>
-  </si>
-  <si>
-    <t>QAA주름와샤</t>
-  </si>
-  <si>
-    <t>SUS304Ø53-Ø36</t>
-  </si>
-  <si>
     <t>51069NO</t>
   </si>
   <si>
@@ -312,515 +90,833 @@
     <t>SUS304 T/S-2 TH 컷팅 우산머리</t>
   </si>
   <si>
-    <t>61037NA</t>
-  </si>
-  <si>
-    <t>신한세라믹</t>
-  </si>
-  <si>
-    <t>카트리지 35ER,A</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>62004CA</t>
-  </si>
-  <si>
     <t>대흥티에프</t>
   </si>
   <si>
-    <t>에어레이터+하우징_0.29$ (청색)샤워,겸용</t>
-  </si>
-  <si>
-    <t>C3604BD.POM 수출용</t>
-  </si>
-  <si>
-    <t>71853NO</t>
-  </si>
-  <si>
     <t>제일피앤씨</t>
   </si>
   <si>
-    <t>LF7375,LF1500 IN BOX</t>
-  </si>
-  <si>
-    <t>430x190x65 ( 무지 )</t>
-  </si>
-  <si>
-    <t>71854NO</t>
-  </si>
-  <si>
-    <t>LF7375,LF1500 C/T_8</t>
-  </si>
-  <si>
-    <t>450x405x290 ( 무지 )</t>
-  </si>
-  <si>
-    <t>71855NO</t>
-  </si>
-  <si>
-    <t>LF7375,LF1500 PAD_1</t>
-  </si>
-  <si>
-    <t>310*130*40</t>
-  </si>
-  <si>
-    <t>72006NO</t>
-  </si>
-  <si>
     <t>서호테크</t>
   </si>
   <si>
-    <t>비닐 25*40</t>
-  </si>
-  <si>
-    <t>250x400x0.05t-1.100</t>
-  </si>
-  <si>
-    <t>73062XO</t>
-  </si>
-  <si>
     <t>삼보인쇄사</t>
   </si>
   <si>
-    <t>QAC취급설명서</t>
-  </si>
-  <si>
-    <t>73062YO</t>
-  </si>
-  <si>
-    <t>QAC시공설명서</t>
-  </si>
-  <si>
-    <t>74014NO</t>
-  </si>
-  <si>
     <t>한성시스템</t>
   </si>
   <si>
-    <t>무지라벨 100*145 C/T 스티커</t>
-  </si>
-  <si>
-    <t>ART90ms</t>
-  </si>
-  <si>
-    <t>74021NO</t>
-  </si>
-  <si>
-    <t>화상주의스티커(QAC)</t>
-  </si>
-  <si>
-    <t>ASAHI 25*15MM-은무데드롱지</t>
-  </si>
-  <si>
-    <t>74022NO-1</t>
-  </si>
-  <si>
-    <t>로고용/msPET25+무/27x10x2열</t>
-  </si>
-  <si>
-    <t>은무데드롱지(ASAHI)-인쇄&lt;TNV</t>
-  </si>
-  <si>
-    <t>74092NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INBOX 스티커 </t>
-  </si>
-  <si>
-    <t>100*60</t>
-  </si>
-  <si>
-    <t>74198NO</t>
-  </si>
-  <si>
     <t>현대오피스상사</t>
   </si>
   <si>
-    <t>라벨 냉수 (BLUE)-MOQ20000</t>
-  </si>
-  <si>
-    <t>50*15_고압호스부착</t>
-  </si>
-  <si>
-    <t>74199NO</t>
-  </si>
-  <si>
-    <t>라벨 온수 (RED)-MOQ20000</t>
-  </si>
-  <si>
-    <t>24051CO-E</t>
-  </si>
-  <si>
-    <t>QAC바디파이프</t>
-  </si>
-  <si>
-    <t>24051CO</t>
-  </si>
-  <si>
-    <t>24051NO-D</t>
-  </si>
-  <si>
-    <t>31058BA</t>
-  </si>
-  <si>
-    <t>QAC고압호수635+5-0</t>
-  </si>
-  <si>
-    <t>C3604BD.SUSPE-X</t>
-  </si>
-  <si>
-    <t>31058RA</t>
-  </si>
-  <si>
-    <t>11400CO</t>
-  </si>
-  <si>
-    <t>QAB바디케이스_도금</t>
-  </si>
-  <si>
-    <t>11400NO</t>
-  </si>
-  <si>
-    <t>QAB바디케이스_NTR</t>
-  </si>
-  <si>
-    <t>11400NO-D</t>
-  </si>
-  <si>
-    <t>QAB바디케이스_연마</t>
-  </si>
-  <si>
-    <t>11401CO</t>
-  </si>
-  <si>
-    <t>QAB헤드케이스_도금</t>
-  </si>
-  <si>
-    <t>11401NO</t>
-  </si>
-  <si>
-    <t>QAB헤드케이스_NTR</t>
-  </si>
-  <si>
-    <t>11401NO-D</t>
-  </si>
-  <si>
-    <t>QAB헤드케이스_연마</t>
-  </si>
-  <si>
-    <t>12008NO</t>
-  </si>
-  <si>
-    <t>옥성CNC</t>
-  </si>
-  <si>
-    <t>호수가이드</t>
-  </si>
-  <si>
-    <t>POM</t>
-  </si>
-  <si>
-    <t>12038NA</t>
-  </si>
-  <si>
-    <t>이엘엔터프라이즈</t>
-  </si>
-  <si>
-    <t>체크밸브Ø15mm_청색</t>
-  </si>
-  <si>
-    <t>역류방지기 15*16</t>
-  </si>
-  <si>
-    <t>12054NO</t>
-  </si>
-  <si>
-    <t>스파우트부쉬_좌-QAB</t>
-  </si>
-  <si>
-    <t>GF10%</t>
-  </si>
-  <si>
-    <t>12055NO</t>
-  </si>
-  <si>
-    <t>스파우트부쉬_우-QAB</t>
-  </si>
-  <si>
-    <t>14001NO</t>
-  </si>
-  <si>
-    <t>이주테크</t>
-  </si>
-  <si>
-    <t>외캡U1"</t>
-  </si>
-  <si>
-    <t>PE 청색</t>
-  </si>
-  <si>
-    <t>18002NO</t>
-  </si>
-  <si>
-    <t>QAA헤드부쉬</t>
-  </si>
-  <si>
-    <t>polyketone GF15%</t>
-  </si>
-  <si>
-    <t>18006NO</t>
-  </si>
-  <si>
-    <t>커플러 바디_후가공</t>
-  </si>
-  <si>
-    <t>18006NO-K</t>
-  </si>
-  <si>
-    <t>커플러 바디_가공</t>
-  </si>
-  <si>
-    <t>SUS(디앤이--수성가공)</t>
-  </si>
-  <si>
-    <t>18007NO</t>
-  </si>
-  <si>
-    <t>커플러 캡</t>
-  </si>
-  <si>
-    <t>18008NO</t>
-  </si>
-  <si>
-    <t>QAB이너헤드</t>
-  </si>
-  <si>
-    <t>22097NO</t>
-  </si>
-  <si>
-    <t>QAB무게추set</t>
-  </si>
-  <si>
-    <t>22098NO</t>
-  </si>
-  <si>
-    <t>QAB이너바디</t>
-  </si>
-  <si>
-    <t>C3771BD_W37xTH20_M10x1.0</t>
-  </si>
-  <si>
-    <t>22100NO</t>
-  </si>
-  <si>
-    <t>QAB샹크</t>
-  </si>
-  <si>
-    <t>C3771BD_M40x1.25_M35x1.5</t>
-  </si>
-  <si>
-    <t>23005NA</t>
-  </si>
-  <si>
     <t>에이치테크</t>
   </si>
   <si>
-    <t>역지변컨넥터세트조립</t>
-  </si>
-  <si>
-    <t>비닐10*13+패킹2+체크밸브+외캡2 사급+역지변2</t>
-  </si>
-  <si>
-    <t>23186NO</t>
-  </si>
-  <si>
-    <t>대도금속공업사</t>
-  </si>
-  <si>
-    <t>QAB바디케이스인서트</t>
-  </si>
-  <si>
-    <t>23199NO</t>
-  </si>
-  <si>
-    <t>QAB샤워호스연결니쁠</t>
-  </si>
-  <si>
-    <t>M15xM13</t>
-  </si>
-  <si>
-    <t>25016NO</t>
-  </si>
-  <si>
     <t>수입오동철</t>
-  </si>
-  <si>
-    <t>믹싱파이프</t>
-  </si>
-  <si>
-    <t>31024BA</t>
-  </si>
-  <si>
-    <t>고압호수481+5-0-QAB</t>
-  </si>
-  <si>
-    <t>31024RA</t>
-  </si>
-  <si>
-    <t>33009NA</t>
-  </si>
-  <si>
-    <t>다원산업</t>
-  </si>
-  <si>
-    <t>QAB메탈호스 1.1M</t>
-  </si>
-  <si>
-    <t>V패킹사급해야됨</t>
-  </si>
-  <si>
-    <t>41029NO</t>
-  </si>
-  <si>
-    <t>컨넥터평패킹_12*7*3T</t>
-  </si>
-  <si>
-    <t>12x7x3T</t>
-  </si>
-  <si>
-    <t>41033NA</t>
-  </si>
-  <si>
-    <t>테일너트패킹</t>
-  </si>
-  <si>
-    <t>#60</t>
-  </si>
-  <si>
-    <t>41077NO</t>
-  </si>
-  <si>
-    <t>QAA메탈호스 V패킹</t>
-  </si>
-  <si>
-    <t>코진,다원사급해야됨</t>
-  </si>
-  <si>
-    <t>41078NO</t>
-  </si>
-  <si>
-    <t>원터치커플러패킹</t>
-  </si>
-  <si>
-    <t>16*10*2.5</t>
-  </si>
-  <si>
-    <t>41079NO</t>
-  </si>
-  <si>
-    <t>역지변컨넥터평패킹</t>
-  </si>
-  <si>
-    <t>18.5*11.5*2</t>
-  </si>
-  <si>
-    <t>41616NO</t>
-  </si>
-  <si>
-    <t>오링 P-11</t>
-  </si>
-  <si>
-    <t>NBRØ10.8x2.4 (티볼트겸용)</t>
-  </si>
-  <si>
-    <t>41654NO</t>
-  </si>
-  <si>
-    <t>오링 AN-028</t>
-  </si>
-  <si>
-    <t>41655NO</t>
-  </si>
-  <si>
-    <t>오링 AN-017</t>
-  </si>
-  <si>
-    <t>51051NO-1</t>
-  </si>
-  <si>
-    <t>QAB무게추 M/S PH4-10mm코팅안함</t>
-  </si>
-  <si>
-    <t>SUS304 M/S PH(코팅X)</t>
-  </si>
-  <si>
-    <t>51139NO</t>
-  </si>
-  <si>
-    <t>볼코리아</t>
-  </si>
-  <si>
-    <t>커플러 볼</t>
-  </si>
-  <si>
-    <t>3.57mm</t>
-  </si>
-  <si>
-    <t>51140NO</t>
-  </si>
-  <si>
-    <t>해주정밀</t>
-  </si>
-  <si>
-    <t>커플러 스프링(QAA)</t>
-  </si>
-  <si>
-    <t>51141NO</t>
-  </si>
-  <si>
-    <t>일호앤시티</t>
-  </si>
-  <si>
-    <t>BODY BASE HOLDER</t>
-  </si>
-  <si>
-    <t>QAB</t>
-  </si>
-  <si>
-    <t>51146NO</t>
-  </si>
-  <si>
-    <t>이너바디 렌치볼트(QAB)</t>
-  </si>
-  <si>
-    <t>M3*0.5P*6_둥근머리</t>
-  </si>
-  <si>
-    <t>73061XO</t>
-  </si>
-  <si>
-    <t>QAB취급설명서</t>
-  </si>
-  <si>
-    <t>73061YO</t>
-  </si>
-  <si>
-    <t>QAB시공설명서</t>
-  </si>
-  <si>
-    <t>74208NO</t>
-  </si>
-  <si>
-    <t>QAA샤워헤드몸통분사주의라벨</t>
-  </si>
-  <si>
-    <t>msPET25+무_20*20</t>
   </si>
   <si>
     <t>EA</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABS+Cr(PNC1)</t>
+  </si>
+  <si>
+    <t>수입JHY</t>
+  </si>
+  <si>
+    <t>41607NO</t>
+  </si>
+  <si>
+    <t>오링 P-9</t>
+  </si>
+  <si>
+    <t>Ø8.8x1.9</t>
+  </si>
+  <si>
+    <t>72017NO</t>
+  </si>
+  <si>
+    <t>비닐 15*12 ( 지퍼 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15*12  </t>
+  </si>
+  <si>
+    <t>3600:67,1800:86,1500:90</t>
+  </si>
+  <si>
+    <t>74023NO</t>
+  </si>
+  <si>
+    <t>LOT스티커 27mmx10mm</t>
+  </si>
+  <si>
+    <t>은무데드롱지(3열)</t>
+  </si>
+  <si>
+    <t>01016CA</t>
+  </si>
+  <si>
+    <t>LF1500(KLO150) 몸통 반제품</t>
+  </si>
+  <si>
+    <t>(몸통+핸들+카트리지+락링+락링커버+에어레이터+스터드볼트+베이스링세트) 중량 793g</t>
+  </si>
+  <si>
+    <t>11030CO</t>
+  </si>
+  <si>
+    <t>삼각핸들</t>
+  </si>
+  <si>
+    <t>11065CO</t>
+  </si>
+  <si>
+    <t>세종기업/삼일공사</t>
+  </si>
+  <si>
+    <t>세종왕Ø60x10</t>
+  </si>
+  <si>
+    <t>11076NO</t>
+  </si>
+  <si>
+    <t>디케이테크</t>
+  </si>
+  <si>
+    <t>LF8200핸들캡_W</t>
+  </si>
+  <si>
+    <t>ABS W</t>
+  </si>
+  <si>
+    <t>11077NO</t>
+  </si>
+  <si>
+    <t>락링커버_W (LF8200용)</t>
+  </si>
+  <si>
+    <t>11078NO</t>
+  </si>
+  <si>
+    <t>LF8200상커버_W</t>
+  </si>
+  <si>
+    <t>11080NO</t>
+  </si>
+  <si>
+    <t>LF8200T하커버(히톤)_W</t>
+  </si>
+  <si>
+    <t>ABS-W</t>
+  </si>
+  <si>
+    <t>11083KA</t>
+  </si>
+  <si>
+    <t>무테일너트SET</t>
+  </si>
+  <si>
+    <t>ABS-BLACK</t>
+  </si>
+  <si>
+    <t>11083KO</t>
+  </si>
+  <si>
+    <t>무테일너트_패킹제외</t>
+  </si>
+  <si>
+    <t>11091KO</t>
+  </si>
+  <si>
+    <t>LF1217KM설치공구</t>
+  </si>
+  <si>
+    <t>11296KO</t>
+  </si>
+  <si>
+    <t>원홀조임공구_A</t>
+  </si>
+  <si>
+    <t>스터드볼트너트</t>
+  </si>
+  <si>
+    <t>11324NO</t>
+  </si>
+  <si>
+    <t>LF8200핸들 -W</t>
+  </si>
+  <si>
+    <t>12017NO</t>
+  </si>
+  <si>
+    <t>LF8200토수구</t>
+  </si>
+  <si>
+    <t>POM FG25% + P-9</t>
+  </si>
+  <si>
+    <t>12038NA</t>
+  </si>
+  <si>
+    <t>이엘엔터프라이즈</t>
+  </si>
+  <si>
+    <t>체크밸브Ø15mm_청색</t>
+  </si>
+  <si>
+    <t>역류방지기 15*16</t>
+  </si>
+  <si>
+    <t>13001NO</t>
+  </si>
+  <si>
+    <t>성진기업</t>
+  </si>
+  <si>
+    <t>LF13Ø18슬립와샤</t>
+  </si>
+  <si>
+    <t>PE(백색) 18X13.5X0.25t</t>
+  </si>
+  <si>
+    <t>21062CO-E</t>
+  </si>
+  <si>
+    <t>태희금속</t>
+  </si>
+  <si>
+    <t>2다용도꼭지몸통주물</t>
+  </si>
+  <si>
+    <t>Cr(BNC1)</t>
+  </si>
+  <si>
+    <t>21062NO</t>
+  </si>
+  <si>
+    <t>성진밸브산업</t>
+  </si>
+  <si>
+    <t>2다용도꼭지몸통주물_2.0</t>
+  </si>
+  <si>
+    <t>CAC203 중량:0.458Kg가공비350</t>
+  </si>
+  <si>
+    <t>21062NO-C</t>
+  </si>
+  <si>
+    <t>대림금속</t>
+  </si>
+  <si>
+    <t>2다용도꼭지몸통주물_0.465</t>
+  </si>
+  <si>
+    <t>21062NO-K</t>
+  </si>
+  <si>
+    <t>2다용도꼭지몸통주물_가공</t>
+  </si>
+  <si>
+    <t>21064NO</t>
+  </si>
+  <si>
+    <t>8200주물몸통_2.1</t>
+  </si>
+  <si>
+    <t>CAC203 중량:0.385Kg</t>
+  </si>
+  <si>
+    <t>21064NO-C</t>
+  </si>
+  <si>
+    <t>8200주물몸통_0.385</t>
+  </si>
+  <si>
+    <t>21064NO-K</t>
+  </si>
+  <si>
+    <t>8200주물몸통</t>
+  </si>
+  <si>
+    <t>CAC203</t>
+  </si>
+  <si>
+    <t>21071CO-E</t>
+  </si>
+  <si>
+    <t>단수전몸통-LF17KM</t>
+  </si>
+  <si>
+    <t>CAC203PNC1</t>
+  </si>
+  <si>
+    <t>21071NO</t>
+  </si>
+  <si>
+    <t>단수전몸통_2.0-LF17KM</t>
+  </si>
+  <si>
+    <t>CAC203 중량:0.430kg</t>
+  </si>
+  <si>
+    <t>21071NO-C</t>
+  </si>
+  <si>
+    <t>단수전몸통_0.430</t>
+  </si>
+  <si>
+    <t>21071NO-D</t>
+  </si>
+  <si>
+    <t>대용연마</t>
+  </si>
+  <si>
+    <t>21071NO-K</t>
+  </si>
+  <si>
+    <t>단수전몸통</t>
+  </si>
+  <si>
+    <t>22001NO</t>
+  </si>
+  <si>
+    <t>코진테크</t>
+  </si>
+  <si>
+    <t>LF13테일너트Ø13.5</t>
+  </si>
+  <si>
+    <t>C3604BD바렐 무도금</t>
+  </si>
+  <si>
+    <t>22004NO</t>
+  </si>
+  <si>
+    <t>대도금속공업사</t>
+  </si>
+  <si>
+    <t>4"샹크(LF17KM)</t>
+  </si>
+  <si>
+    <t>C3771BE+오링AN-015</t>
+  </si>
+  <si>
+    <t>22012CO</t>
+  </si>
+  <si>
+    <t>꼭지대Ø19x1줄(분리형스핀들)</t>
+  </si>
+  <si>
+    <t>C3604BDM5x0.8x43mm+Cr</t>
+  </si>
+  <si>
+    <t>22021NO</t>
+  </si>
+  <si>
+    <t>대동테크</t>
+  </si>
+  <si>
+    <t>Ø35락링(수출용)</t>
+  </si>
+  <si>
+    <t>C3771BEØ23 83g</t>
+  </si>
+  <si>
+    <t>22026NO</t>
+  </si>
+  <si>
+    <t>역지샹크(황동LF8200T用)</t>
+  </si>
+  <si>
+    <t>C3771BEØ21+AN-015</t>
+  </si>
+  <si>
+    <t>23003CO</t>
+  </si>
+  <si>
+    <t>누르게 대면거리 26MM</t>
+  </si>
+  <si>
+    <t>도금Cr</t>
+  </si>
+  <si>
+    <t>23009BO</t>
+  </si>
+  <si>
+    <t>평화인쇄</t>
+  </si>
+  <si>
+    <t>캡볼트(로렛트)_청</t>
+  </si>
+  <si>
+    <t>M5x0.8 + 에폭스티커</t>
+  </si>
+  <si>
+    <t>23009CO-E</t>
+  </si>
+  <si>
+    <t>캡볼트(로렛트)</t>
+  </si>
+  <si>
+    <t>M5x0.8</t>
+  </si>
+  <si>
+    <t>23009NO</t>
+  </si>
+  <si>
+    <t>23041CO</t>
+  </si>
+  <si>
+    <t>2다용도전환뭉치스핀들</t>
+  </si>
+  <si>
+    <t>오링:P-6(2개)</t>
+  </si>
+  <si>
+    <t>23042CO</t>
+  </si>
+  <si>
+    <t>2다용도전환뭉치하우징</t>
+  </si>
+  <si>
+    <t>오링:15*2</t>
+  </si>
+  <si>
+    <t>23043CO-E</t>
+  </si>
+  <si>
+    <t>2다용도마개</t>
+  </si>
+  <si>
+    <t>Cr(BNC1) G1/2x14TH</t>
+  </si>
+  <si>
+    <t>23043NO</t>
+  </si>
+  <si>
+    <t>대진금속</t>
+  </si>
+  <si>
+    <t>2다용도마개 MOQ:1000</t>
+  </si>
+  <si>
+    <t>Cr(BNC1) + 오링 AN-114</t>
+  </si>
+  <si>
+    <t>23043NO-D</t>
+  </si>
+  <si>
+    <t>23086CO</t>
+  </si>
+  <si>
+    <t>히톤</t>
+  </si>
+  <si>
+    <t>C3604Ø6x13xM4x0.7</t>
+  </si>
+  <si>
+    <t>23086CO-E</t>
+  </si>
+  <si>
+    <t>31056BA</t>
+  </si>
+  <si>
+    <t>베스트엔퍼스트</t>
+  </si>
+  <si>
+    <t>QAA고압호수412+5-0</t>
+  </si>
+  <si>
+    <t>C3604BD.SUSPE-X</t>
+  </si>
+  <si>
+    <t>31056RA</t>
+  </si>
+  <si>
+    <t>41010NO</t>
+  </si>
+  <si>
+    <t>평패킹_18*12*4T-12.17KM</t>
+  </si>
+  <si>
+    <t>18x12x4T</t>
+  </si>
+  <si>
+    <t>41013NO</t>
+  </si>
+  <si>
+    <t>LF캡너트△패킹(대)</t>
+  </si>
+  <si>
+    <t>NBR</t>
+  </si>
+  <si>
+    <t>41024NO</t>
+  </si>
+  <si>
+    <t>에어레이터평패킹21x15x2.4t</t>
+  </si>
+  <si>
+    <t>NBR외Ø21x내Ø15x두2.4</t>
+  </si>
+  <si>
+    <t>41060NO</t>
+  </si>
+  <si>
+    <t>평패킹_38*26*3T-LF17</t>
+  </si>
+  <si>
+    <t>NBR 38*26*3</t>
+  </si>
+  <si>
+    <t>41601NO</t>
+  </si>
+  <si>
+    <t>오링 15*2</t>
+  </si>
+  <si>
+    <t>NBRØ15x2</t>
+  </si>
+  <si>
+    <t>41603NO</t>
+  </si>
+  <si>
+    <t>오링 AN-015</t>
+  </si>
+  <si>
+    <t>NBRØ14x1.78</t>
+  </si>
+  <si>
+    <t>41611NO</t>
+  </si>
+  <si>
+    <t>오링 P-6</t>
+  </si>
+  <si>
+    <t>Ø5.8x1.9</t>
+  </si>
+  <si>
+    <t>41615NO</t>
+  </si>
+  <si>
+    <t>오링 AN-114</t>
+  </si>
+  <si>
+    <t>Ø15.54x2.62</t>
+  </si>
+  <si>
+    <t>42002NO</t>
+  </si>
+  <si>
+    <t>절수디스크</t>
+  </si>
+  <si>
+    <t>C3604BD+EPDM90도</t>
+  </si>
+  <si>
+    <t>42003NO</t>
+  </si>
+  <si>
+    <t>디스크패킹_14.2*4*3T</t>
+  </si>
+  <si>
+    <t>EPDM90도(14.2X4X3t)</t>
+  </si>
+  <si>
+    <t>43007NO</t>
+  </si>
+  <si>
+    <t>EVA패킹_36*20.5*3T-17KM</t>
+  </si>
+  <si>
+    <t>Ø36xØ20.5x3tEVA</t>
+  </si>
+  <si>
+    <t>43017NO</t>
+  </si>
+  <si>
+    <t>SEAT PACKING-LF8200</t>
+  </si>
+  <si>
+    <t>EVA1.5t</t>
+  </si>
+  <si>
+    <t>51007NO</t>
+  </si>
+  <si>
+    <t>무두볼트 5*8</t>
+  </si>
+  <si>
+    <t>SUS304M5x.8-8mm</t>
+  </si>
+  <si>
+    <t>51009NO</t>
+  </si>
+  <si>
+    <t>삼일공사</t>
+  </si>
+  <si>
+    <t>캡너트와샤_19*10*1T</t>
+  </si>
+  <si>
+    <t>SUS304Ø19xØ10x1T(MOQ10000개)</t>
+  </si>
+  <si>
+    <t>51051NO</t>
+  </si>
+  <si>
+    <t>디스크볼트 M/S PH4-10mm 코팅</t>
+  </si>
+  <si>
+    <t>SUS304 M/S PH(코팅)</t>
+  </si>
+  <si>
+    <t>51112NO</t>
+  </si>
+  <si>
+    <t>와샤_38.8x21x2T</t>
+  </si>
+  <si>
+    <t>SUS304 주)신일화스너 3/4</t>
+  </si>
+  <si>
+    <t>52004CO</t>
+  </si>
+  <si>
+    <t>킴스핸들_JD-14</t>
+  </si>
+  <si>
+    <t>무인쇄</t>
+  </si>
+  <si>
+    <t>61031NA</t>
+  </si>
+  <si>
+    <t>90도세라믹_$1.1</t>
+  </si>
+  <si>
+    <t>61037NA</t>
+  </si>
+  <si>
+    <t>신한세라믹</t>
+  </si>
+  <si>
+    <t>카트리지 35ER,A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>62004CA</t>
+  </si>
+  <si>
+    <t>에어레이터+하우징_0.29$ (청색)샤워,겸용</t>
+  </si>
+  <si>
+    <t>C3604BD.POM 수출용</t>
+  </si>
+  <si>
+    <t>62040CA</t>
+  </si>
+  <si>
+    <t>네오펠</t>
+  </si>
+  <si>
+    <t>LF17KM에어레이터</t>
+  </si>
+  <si>
+    <t>M18*1V(44.3034.03301)</t>
+  </si>
+  <si>
+    <t>71004IN</t>
+  </si>
+  <si>
+    <t>LF4181 INBOX</t>
+  </si>
+  <si>
+    <t>160x150x155 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71004ON</t>
+  </si>
+  <si>
+    <t>LF4181 C/T_12</t>
+  </si>
+  <si>
+    <t>500x315x333 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71008IN</t>
+  </si>
+  <si>
+    <t>LF1217KM IN BOX_1</t>
+  </si>
+  <si>
+    <t>235x115x60 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71008ON</t>
+  </si>
+  <si>
+    <t>LF1217KM C/T_30</t>
+  </si>
+  <si>
+    <t>490x375x340 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71635IN</t>
+  </si>
+  <si>
+    <t>CF248KM INBOX_1</t>
+  </si>
+  <si>
+    <t>140x105x55 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71635ON</t>
+  </si>
+  <si>
+    <t>CF248KM C/T_36</t>
+  </si>
+  <si>
+    <t>450x335x250 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71853NO</t>
+  </si>
+  <si>
+    <t>LF7375,LF1500 IN BOX</t>
+  </si>
+  <si>
+    <t>430x190x65 ( 무지 )</t>
+  </si>
+  <si>
+    <t>71854NO</t>
+  </si>
+  <si>
+    <t>LF7375,LF1500 C/T_8</t>
+  </si>
+  <si>
+    <t>450x405x290 ( 무지 )</t>
+  </si>
+  <si>
+    <t>72001NO</t>
+  </si>
+  <si>
+    <t>일석공업사</t>
+  </si>
+  <si>
+    <t>발포지 150*300*1T</t>
+  </si>
+  <si>
+    <t>150x300x1t발포</t>
+  </si>
+  <si>
+    <t>72003NO</t>
+  </si>
+  <si>
+    <t>발포지 250*300*1T</t>
+  </si>
+  <si>
+    <t>250x300x1t 발포</t>
+  </si>
+  <si>
+    <t>72006NO</t>
+  </si>
+  <si>
+    <t>비닐 25*40</t>
+  </si>
+  <si>
+    <t>250x400x0.05t-1.100</t>
+  </si>
+  <si>
+    <t>73005XO</t>
+  </si>
+  <si>
+    <t>LF8200 취급설명서</t>
+  </si>
+  <si>
+    <t>73005YO</t>
+  </si>
+  <si>
+    <t>LF8200 시공설명서</t>
+  </si>
+  <si>
+    <t>73097NO</t>
+  </si>
+  <si>
+    <t>LF1500 시공설명서</t>
+  </si>
+  <si>
+    <t>A3반접지양면흑백미색모조</t>
+  </si>
+  <si>
+    <t>73098NO</t>
+  </si>
+  <si>
+    <t>LF1500 취급설명서</t>
+  </si>
+  <si>
+    <t>A4중철8P흑백미색모조</t>
+  </si>
+  <si>
+    <t>74002NO</t>
+  </si>
+  <si>
+    <t>INBOX/ART90ms/60*40</t>
+  </si>
+  <si>
+    <t>74014NO</t>
+  </si>
+  <si>
+    <t>무지라벨 100*145 C/T 스티커</t>
+  </si>
+  <si>
+    <t>ART90ms</t>
+  </si>
+  <si>
+    <t>74022NO-1</t>
+  </si>
+  <si>
+    <t>로고용/msPET25+무/27x10x2열</t>
+  </si>
+  <si>
+    <t>은무데드롱지(ASAHI)-인쇄&lt;TNV</t>
+  </si>
+  <si>
+    <t>74143NO</t>
+  </si>
+  <si>
+    <t>LF8200라벨_C/T BOX_CA</t>
+  </si>
+  <si>
+    <t>ART90ms/100*145</t>
+  </si>
+  <si>
+    <t>74187NO</t>
+  </si>
+  <si>
+    <t>LF8200라벨_IN BOX (파란)</t>
+  </si>
+  <si>
+    <t>ART90ms/100*60</t>
+  </si>
+  <si>
+    <t>74198NO</t>
+  </si>
+  <si>
+    <t>라벨 냉수 (BLUE)-MOQ20000</t>
+  </si>
+  <si>
+    <t>50*15_고압호스부착</t>
+  </si>
+  <si>
+    <t>74199NO</t>
+  </si>
+  <si>
+    <t>라벨 온수 (RED)-MOQ20000</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -1308,22 +1404,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
-        <v>200</v>
+        <v>12889</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -1332,22 +1428,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1356,22 +1452,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1380,1579 +1476,1579 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>270</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>740</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>740</v>
+        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>475</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>475</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>260</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>260</v>
+        <v>900</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>120</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>120</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>130</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>130</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>1480</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>2450</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>800</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>710</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
+        <v>92</v>
+      </c>
+      <c r="D22">
+        <v>0.46500000000000002</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>640</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F24">
-        <v>320</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
-      </c>
-      <c r="D25" t="s">
-        <v>166</v>
+        <v>99</v>
+      </c>
+      <c r="D25">
+        <v>0.38500000000000001</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>250</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F26">
-        <v>210</v>
+        <v>850</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>210</v>
+        <v>596</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" t="s">
-        <v>178</v>
+        <v>110</v>
+      </c>
+      <c r="D29">
+        <v>0.43</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>215</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>407</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F31">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>260</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F33">
-        <v>450</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>537</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>955</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36">
-        <v>0.38200000000000001</v>
+        <v>131</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>5233.018</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>650</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>2000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>1500</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>11935</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>800</v>
+        <v>650</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>389</v>
+        <v>790</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F43">
-        <v>3650</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F44">
-        <v>920</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F45">
-        <v>920</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>1462</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>3657</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="D48" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>2445</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>752</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>525</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>670</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F52">
-        <v>500</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F53">
-        <v>1100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F54">
-        <v>8600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F55">
-        <v>1000</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F56">
-        <v>1208</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>210</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F57">
-        <v>2638</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F58">
-        <v>2638</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F59">
-        <v>2835</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F60">
-        <v>2835</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F61">
-        <v>3000</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>69</v>
+        <v>199</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F62">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>201</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F63">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D64" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F64">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D65" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F65">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F66">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F67">
-        <v>57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F68">
-        <v>27</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F69">
-        <v>22</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D70" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F70">
-        <v>22</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="C71" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D71" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F71">
-        <v>16</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F72">
-        <v>19</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>229</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F73">
-        <v>14</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>232</v>
+      </c>
+      <c r="B74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" t="s">
+        <v>233</v>
+      </c>
+      <c r="D74" t="s">
         <v>234</v>
       </c>
-      <c r="B74" t="s">
-        <v>67</v>
-      </c>
-      <c r="C74" t="s">
-        <v>235</v>
-      </c>
-      <c r="D74" t="s">
-        <v>45</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F74">
-        <v>33</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
         <v>236</v>
       </c>
-      <c r="B75" t="s">
-        <v>67</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>237</v>
       </c>
-      <c r="D75" t="s">
-        <v>45</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F75">
-        <v>15</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>239</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F76">
-        <v>52</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F77">
-        <v>52</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>246</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F78">
-        <v>18</v>
+        <v>150</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="D79" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F79">
-        <v>19</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>86</v>
+        <v>250</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="C80" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="D80" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F80">
-        <v>220</v>
+        <v>483</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
+        <v>254</v>
       </c>
       <c r="D81" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F81">
-        <v>220</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="C82" t="s">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="D82" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F82">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F83">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C84" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D85" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F85">
         <v>30</v>
@@ -2960,603 +3056,1602 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>251</v>
+        <v>35</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F86">
-        <v>1500</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D87" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F87">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>268</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F88">
-        <v>2110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>270</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="D89" t="s">
-        <v>96</v>
+        <v>272</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F89">
-        <v>2110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>273</v>
       </c>
       <c r="B90" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F90">
-        <v>320</v>
+        <v>156</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>277</v>
       </c>
       <c r="D91" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F91">
-        <v>320</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F92">
-        <v>483</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>278</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="D93" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F93">
-        <v>483</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>105</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F94">
-        <v>1486</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>281</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F95">
-        <v>1486</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C96" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F96">
-        <v>158</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>285</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>286</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F97">
-        <v>158</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>287</v>
       </c>
       <c r="B98" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="C98" t="s">
-        <v>113</v>
+        <v>288</v>
       </c>
       <c r="D98" t="s">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F98">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>291</v>
       </c>
       <c r="D99" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F99">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="B100" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>292</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="F100">
-        <v>170</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>257</v>
-      </c>
-      <c r="B101" t="s">
-        <v>116</v>
-      </c>
-      <c r="C101" t="s">
-        <v>258</v>
-      </c>
-      <c r="D101" t="s">
-        <v>45</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F101">
-        <v>98</v>
-      </c>
+      <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>115</v>
-      </c>
-      <c r="B102" t="s">
-        <v>116</v>
-      </c>
-      <c r="C102" t="s">
-        <v>117</v>
-      </c>
-      <c r="D102" t="s">
-        <v>45</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F102">
-        <v>101</v>
-      </c>
+      <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>118</v>
-      </c>
-      <c r="B103" t="s">
-        <v>116</v>
-      </c>
-      <c r="C103" t="s">
-        <v>119</v>
-      </c>
-      <c r="D103" t="s">
-        <v>45</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F103">
-        <v>60</v>
-      </c>
+      <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>120</v>
-      </c>
-      <c r="B104" t="s">
-        <v>121</v>
-      </c>
-      <c r="C104" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" t="s">
-        <v>123</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F104">
-        <v>22</v>
-      </c>
+      <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>120</v>
-      </c>
-      <c r="B105" t="s">
-        <v>121</v>
-      </c>
-      <c r="C105" t="s">
-        <v>122</v>
-      </c>
-      <c r="D105" t="s">
-        <v>123</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F105">
-        <v>22</v>
-      </c>
+      <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>124</v>
-      </c>
-      <c r="B106" t="s">
-        <v>121</v>
-      </c>
-      <c r="C106" t="s">
-        <v>125</v>
-      </c>
-      <c r="D106" t="s">
-        <v>126</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F106">
-        <v>5</v>
-      </c>
+      <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>127</v>
-      </c>
-      <c r="B107" t="s">
-        <v>121</v>
-      </c>
-      <c r="C107" t="s">
-        <v>128</v>
-      </c>
-      <c r="D107" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F107">
-        <v>6</v>
-      </c>
+      <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>127</v>
-      </c>
-      <c r="B108" t="s">
-        <v>121</v>
-      </c>
-      <c r="C108" t="s">
-        <v>128</v>
-      </c>
-      <c r="D108" t="s">
-        <v>129</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F108">
-        <v>6</v>
-      </c>
+      <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>130</v>
-      </c>
-      <c r="B109" t="s">
-        <v>121</v>
-      </c>
-      <c r="C109" t="s">
-        <v>131</v>
-      </c>
-      <c r="D109" t="s">
-        <v>132</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F109">
-        <v>18</v>
-      </c>
+      <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>130</v>
-      </c>
-      <c r="B110" t="s">
-        <v>121</v>
-      </c>
-      <c r="C110" t="s">
-        <v>131</v>
-      </c>
-      <c r="D110" t="s">
-        <v>132</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F110">
-        <v>18</v>
-      </c>
+      <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>133</v>
-      </c>
-      <c r="B111" t="s">
-        <v>134</v>
-      </c>
-      <c r="C111" t="s">
-        <v>135</v>
-      </c>
-      <c r="D111" t="s">
-        <v>136</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F111">
-        <v>6</v>
-      </c>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>133</v>
-      </c>
-      <c r="B112" t="s">
-        <v>134</v>
-      </c>
-      <c r="C112" t="s">
-        <v>135</v>
-      </c>
-      <c r="D112" t="s">
-        <v>136</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F112">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>137</v>
-      </c>
-      <c r="B113" t="s">
-        <v>134</v>
-      </c>
-      <c r="C113" t="s">
-        <v>138</v>
-      </c>
-      <c r="D113" t="s">
-        <v>136</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F113">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>137</v>
-      </c>
-      <c r="B114" t="s">
-        <v>134</v>
-      </c>
-      <c r="C114" t="s">
-        <v>138</v>
-      </c>
-      <c r="D114" t="s">
-        <v>136</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F114">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>259</v>
-      </c>
-      <c r="B115" t="s">
-        <v>121</v>
-      </c>
-      <c r="C115" t="s">
-        <v>260</v>
-      </c>
-      <c r="D115" t="s">
-        <v>261</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F115">
-        <v>9</v>
-      </c>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E250" s="3"/>
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E252" s="3"/>
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E253" s="3"/>
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E254" s="3"/>
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E258" s="3"/>
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E259" s="3"/>
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E260" s="3"/>
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E261" s="3"/>
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E262" s="3"/>
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E264" s="3"/>
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E265" s="3"/>
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E266" s="3"/>
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E267" s="3"/>
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E268" s="3"/>
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E269" s="3"/>
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E271" s="3"/>
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E272" s="3"/>
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E273" s="3"/>
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E274" s="3"/>
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E275" s="3"/>
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E276" s="3"/>
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E277" s="3"/>
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E278" s="3"/>
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E279" s="3"/>
+    </row>
+    <row r="280" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E280" s="3"/>
+    </row>
+    <row r="281" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E281" s="3"/>
+    </row>
+    <row r="282" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E282" s="3"/>
+    </row>
+    <row r="283" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E283" s="3"/>
+    </row>
+    <row r="284" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E284" s="3"/>
+    </row>
+    <row r="285" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E285" s="3"/>
+    </row>
+    <row r="286" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E286" s="3"/>
+    </row>
+    <row r="287" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E287" s="3"/>
+    </row>
+    <row r="288" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E288" s="3"/>
+    </row>
+    <row r="289" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E289" s="3"/>
+    </row>
+    <row r="290" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E290" s="3"/>
+    </row>
+    <row r="291" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E291" s="3"/>
+    </row>
+    <row r="292" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E292" s="3"/>
+    </row>
+    <row r="293" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E293" s="3"/>
+    </row>
+    <row r="294" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E294" s="3"/>
+    </row>
+    <row r="295" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E295" s="3"/>
+    </row>
+    <row r="296" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E296" s="3"/>
+    </row>
+    <row r="297" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E297" s="3"/>
+    </row>
+    <row r="298" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E298" s="3"/>
+    </row>
+    <row r="299" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E299" s="3"/>
+    </row>
+    <row r="300" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E300" s="3"/>
+    </row>
+    <row r="301" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E301" s="3"/>
+    </row>
+    <row r="302" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E302" s="3"/>
+    </row>
+    <row r="303" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E303" s="3"/>
+    </row>
+    <row r="304" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E304" s="3"/>
+    </row>
+    <row r="305" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E305" s="3"/>
+    </row>
+    <row r="306" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E306" s="3"/>
+    </row>
+    <row r="307" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E307" s="3"/>
+    </row>
+    <row r="308" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E308" s="3"/>
+    </row>
+    <row r="309" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E310" s="3"/>
+    </row>
+    <row r="311" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E311" s="3"/>
+    </row>
+    <row r="312" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E312" s="3"/>
+    </row>
+    <row r="313" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E313" s="3"/>
+    </row>
+    <row r="314" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E314" s="3"/>
+    </row>
+    <row r="315" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E315" s="3"/>
+    </row>
+    <row r="316" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E316" s="3"/>
+    </row>
+    <row r="317" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E317" s="3"/>
+    </row>
+    <row r="318" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E318" s="3"/>
+    </row>
+    <row r="319" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E319" s="3"/>
+    </row>
+    <row r="320" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E320" s="3"/>
+    </row>
+    <row r="321" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E321" s="3"/>
+    </row>
+    <row r="322" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E322" s="3"/>
+    </row>
+    <row r="323" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E323" s="3"/>
+    </row>
+    <row r="324" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E324" s="3"/>
+    </row>
+    <row r="325" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E325" s="3"/>
+    </row>
+    <row r="326" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E326" s="3"/>
+    </row>
+    <row r="327" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E327" s="3"/>
+    </row>
+    <row r="328" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E328" s="3"/>
+    </row>
+    <row r="329" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E329" s="3"/>
+    </row>
+    <row r="330" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E330" s="3"/>
+    </row>
+    <row r="331" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E331" s="3"/>
+    </row>
+    <row r="332" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E332" s="3"/>
+    </row>
+    <row r="333" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E333" s="3"/>
+    </row>
+    <row r="334" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E334" s="3"/>
+    </row>
+    <row r="335" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E335" s="3"/>
+    </row>
+    <row r="336" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E336" s="3"/>
+    </row>
+    <row r="337" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E337" s="3"/>
+    </row>
+    <row r="338" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E338" s="3"/>
+    </row>
+    <row r="339" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E339" s="3"/>
+    </row>
+    <row r="340" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E340" s="3"/>
+    </row>
+    <row r="341" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E341" s="3"/>
+    </row>
+    <row r="342" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E342" s="3"/>
+    </row>
+    <row r="343" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E343" s="3"/>
+    </row>
+    <row r="344" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E344" s="3"/>
+    </row>
+    <row r="345" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E345" s="3"/>
+    </row>
+    <row r="346" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E346" s="3"/>
+    </row>
+    <row r="347" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E347" s="3"/>
+    </row>
+    <row r="348" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E348" s="3"/>
+    </row>
+    <row r="349" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E349" s="3"/>
+    </row>
+    <row r="350" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E350" s="3"/>
+    </row>
+    <row r="351" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E351" s="3"/>
+    </row>
+    <row r="352" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E352" s="3"/>
+    </row>
+    <row r="353" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E355" s="3"/>
+    </row>
+    <row r="356" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E356" s="3"/>
+    </row>
+    <row r="357" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E357" s="3"/>
+    </row>
+    <row r="358" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E358" s="3"/>
+    </row>
+    <row r="359" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E359" s="3"/>
+    </row>
+    <row r="360" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E360" s="3"/>
+    </row>
+    <row r="361" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E361" s="3"/>
+    </row>
+    <row r="362" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E362" s="3"/>
+    </row>
+    <row r="363" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E363" s="3"/>
+    </row>
+    <row r="364" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E364" s="3"/>
+    </row>
+    <row r="365" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E365" s="3"/>
+    </row>
+    <row r="366" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E366" s="3"/>
+    </row>
+    <row r="367" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E367" s="3"/>
+    </row>
+    <row r="368" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E368" s="3"/>
+    </row>
+    <row r="369" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E369" s="3"/>
+    </row>
+    <row r="370" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E370" s="3"/>
+    </row>
+    <row r="371" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E371" s="3"/>
+    </row>
+    <row r="372" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E372" s="3"/>
+    </row>
+    <row r="373" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E373" s="3"/>
+    </row>
+    <row r="374" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E374" s="3"/>
+    </row>
+    <row r="375" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E375" s="3"/>
+    </row>
+    <row r="376" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E376" s="3"/>
+    </row>
+    <row r="377" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E377" s="3"/>
+    </row>
+    <row r="378" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E378" s="3"/>
+    </row>
+    <row r="379" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E379" s="3"/>
+    </row>
+    <row r="380" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E380" s="3"/>
+    </row>
+    <row r="381" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E381" s="3"/>
+    </row>
+    <row r="382" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E382" s="3"/>
+    </row>
+    <row r="383" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E383" s="3"/>
+    </row>
+    <row r="384" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E384" s="3"/>
+    </row>
+    <row r="385" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E385" s="3"/>
+    </row>
+    <row r="386" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E386" s="3"/>
+    </row>
+    <row r="387" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E387" s="3"/>
+    </row>
+    <row r="388" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E388" s="3"/>
+    </row>
+    <row r="389" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E389" s="3"/>
+    </row>
+    <row r="390" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E390" s="3"/>
+    </row>
+    <row r="391" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E391" s="3"/>
+    </row>
+    <row r="392" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E392" s="3"/>
+    </row>
+    <row r="393" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E393" s="3"/>
+    </row>
+    <row r="394" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E394" s="3"/>
+    </row>
+    <row r="395" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E395" s="3"/>
+    </row>
+    <row r="396" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E396" s="3"/>
+    </row>
+    <row r="397" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E397" s="3"/>
+    </row>
+    <row r="398" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E398" s="3"/>
+    </row>
+    <row r="399" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E399" s="3"/>
+    </row>
+    <row r="400" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E400" s="3"/>
+    </row>
+    <row r="401" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E401" s="3"/>
+    </row>
+    <row r="402" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E402" s="3"/>
+    </row>
+    <row r="403" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E403" s="3"/>
+    </row>
+    <row r="404" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E404" s="3"/>
+    </row>
+    <row r="405" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E405" s="3"/>
+    </row>
+    <row r="406" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E406" s="3"/>
+    </row>
+    <row r="407" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E407" s="3"/>
+    </row>
+    <row r="408" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E408" s="3"/>
+    </row>
+    <row r="409" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E409" s="3"/>
+    </row>
+    <row r="410" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E410" s="3"/>
+    </row>
+    <row r="411" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E411" s="3"/>
+    </row>
+    <row r="412" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E412" s="3"/>
+    </row>
+    <row r="413" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E413" s="3"/>
+    </row>
+    <row r="414" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E414" s="3"/>
+    </row>
+    <row r="415" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E415" s="3"/>
+    </row>
+    <row r="416" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E416" s="3"/>
+    </row>
+    <row r="417" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E417" s="3"/>
+    </row>
+    <row r="418" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E418" s="3"/>
+    </row>
+    <row r="419" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E419" s="3"/>
+    </row>
+    <row r="420" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E420" s="3"/>
+    </row>
+    <row r="421" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E421" s="3"/>
+    </row>
+    <row r="422" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E422" s="3"/>
+    </row>
+    <row r="423" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E423" s="3"/>
+    </row>
+    <row r="424" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E424" s="3"/>
+    </row>
+    <row r="425" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E425" s="3"/>
+    </row>
+    <row r="426" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E426" s="3"/>
+    </row>
+    <row r="427" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E427" s="3"/>
+    </row>
+    <row r="428" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E428" s="3"/>
+    </row>
+    <row r="429" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E429" s="3"/>
+    </row>
+    <row r="430" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E430" s="3"/>
+    </row>
+    <row r="431" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E431" s="3"/>
+    </row>
+    <row r="432" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E432" s="3"/>
+    </row>
+    <row r="433" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E433" s="3"/>
+    </row>
+    <row r="434" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E434" s="3"/>
+    </row>
+    <row r="435" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E435" s="3"/>
+    </row>
+    <row r="436" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E436" s="3"/>
+    </row>
+    <row r="437" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E437" s="3"/>
+    </row>
+    <row r="438" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E438" s="3"/>
+    </row>
+    <row r="439" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E439" s="3"/>
+    </row>
+    <row r="440" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E440" s="3"/>
+    </row>
+    <row r="441" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E441" s="3"/>
+    </row>
+    <row r="442" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E442" s="3"/>
+    </row>
+    <row r="443" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E443" s="3"/>
+    </row>
+    <row r="444" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E444" s="3"/>
+    </row>
+    <row r="445" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E445" s="3"/>
+    </row>
+    <row r="446" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E446" s="3"/>
+    </row>
+    <row r="447" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E447" s="3"/>
+    </row>
+    <row r="448" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E448" s="3"/>
+    </row>
+    <row r="449" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E449" s="3"/>
+    </row>
+    <row r="450" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E450" s="3"/>
+    </row>
+    <row r="451" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E451" s="3"/>
+    </row>
+    <row r="452" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E452" s="3"/>
+    </row>
+    <row r="453" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E453" s="3"/>
+    </row>
+    <row r="454" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E454" s="3"/>
+    </row>
+    <row r="455" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E455" s="3"/>
+    </row>
+    <row r="456" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E456" s="3"/>
+    </row>
+    <row r="457" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E457" s="3"/>
+    </row>
+    <row r="458" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E458" s="3"/>
+    </row>
+    <row r="459" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E459" s="3"/>
+    </row>
+    <row r="460" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E460" s="3"/>
+    </row>
+    <row r="461" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E461" s="3"/>
+    </row>
+    <row r="462" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E462" s="3"/>
+    </row>
+    <row r="463" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E463" s="3"/>
+    </row>
+    <row r="464" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E464" s="3"/>
+    </row>
+    <row r="465" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E465" s="3"/>
+    </row>
+    <row r="466" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E466" s="3"/>
+    </row>
+    <row r="467" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E467" s="3"/>
+    </row>
+    <row r="468" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E468" s="3"/>
+    </row>
+    <row r="469" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E469" s="3"/>
+    </row>
+    <row r="470" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E470" s="3"/>
+    </row>
+    <row r="471" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E471" s="3"/>
+    </row>
+    <row r="472" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E472" s="3"/>
+    </row>
+    <row r="473" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E473" s="3"/>
+    </row>
+    <row r="474" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E474" s="3"/>
+    </row>
+    <row r="475" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E475" s="3"/>
+    </row>
+    <row r="476" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E476" s="3"/>
+    </row>
+    <row r="477" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E477" s="3"/>
+    </row>
+    <row r="478" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E478" s="3"/>
+    </row>
+    <row r="479" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E479" s="3"/>
+    </row>
+    <row r="480" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E480" s="3"/>
+    </row>
+    <row r="481" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E481" s="3"/>
+    </row>
+    <row r="482" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E482" s="3"/>
+    </row>
+    <row r="483" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E483" s="3"/>
+    </row>
+    <row r="484" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E484" s="3"/>
+    </row>
+    <row r="485" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E485" s="3"/>
+    </row>
+    <row r="486" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E486" s="3"/>
+    </row>
+    <row r="487" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E487" s="3"/>
+    </row>
+    <row r="488" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E488" s="3"/>
+    </row>
+    <row r="489" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E489" s="3"/>
+    </row>
+    <row r="490" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E490" s="3"/>
+    </row>
+    <row r="491" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E491" s="3"/>
+    </row>
+    <row r="492" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E492" s="3"/>
+    </row>
+    <row r="493" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E493" s="3"/>
+    </row>
+    <row r="494" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E494" s="3"/>
+    </row>
+    <row r="495" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E495" s="3"/>
+    </row>
+    <row r="496" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E496" s="3"/>
+    </row>
+    <row r="497" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E497" s="3"/>
+    </row>
+    <row r="498" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E498" s="3"/>
+    </row>
+    <row r="499" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E499" s="3"/>
+    </row>
+    <row r="500" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E500" s="3"/>
+    </row>
+    <row r="501" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E501" s="3"/>
+    </row>
+    <row r="502" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E502" s="3"/>
+    </row>
+    <row r="503" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E503" s="3"/>
+    </row>
+    <row r="504" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E504" s="3"/>
+    </row>
+    <row r="505" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E505" s="3"/>
+    </row>
+    <row r="506" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E506" s="3"/>
+    </row>
+    <row r="507" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E507" s="3"/>
+    </row>
+    <row r="508" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E508" s="3"/>
+    </row>
+    <row r="509" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E509" s="3"/>
+    </row>
+    <row r="510" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E510" s="3"/>
+    </row>
+    <row r="511" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E511" s="3"/>
+    </row>
+    <row r="512" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E512" s="3"/>
+    </row>
+    <row r="513" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E513" s="3"/>
+    </row>
+    <row r="514" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E514" s="3"/>
+    </row>
+    <row r="515" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E515" s="3"/>
+    </row>
+    <row r="516" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E516" s="3"/>
+    </row>
+    <row r="517" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E517" s="3"/>
+    </row>
+    <row r="518" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E518" s="3"/>
+    </row>
+    <row r="519" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E519" s="3"/>
+    </row>
+    <row r="520" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E520" s="3"/>
+    </row>
+    <row r="521" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E521" s="3"/>
+    </row>
+    <row r="522" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E522" s="3"/>
+    </row>
+    <row r="523" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E523" s="3"/>
+    </row>
+    <row r="524" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E524" s="3"/>
+    </row>
+    <row r="525" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E525" s="3"/>
+    </row>
+    <row r="526" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E526" s="3"/>
+    </row>
+    <row r="527" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E527" s="3"/>
+    </row>
+    <row r="528" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E528" s="3"/>
+    </row>
+    <row r="529" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E529" s="3"/>
+    </row>
+    <row r="530" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E530" s="3"/>
+    </row>
+    <row r="531" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E531" s="3"/>
+    </row>
+    <row r="532" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E532" s="3"/>
+    </row>
+    <row r="533" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E533" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3565,5 +4660,6 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>